--- a/20250710_req_filtros/doc/Copia de Integración BULK (003).xlsx
+++ b/20250710_req_filtros/doc/Copia de Integración BULK (003).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13500" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Detalle Envíos" sheetId="1" state="hidden" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Detalle envios" sheetId="4" r:id="rId4"/>
     <sheet name="CAsillas Templates" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="217">
   <si>
     <t>Email Destinatario</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>Registro Leido</t>
+  </si>
+  <si>
+    <t>monto_posible_compensar</t>
   </si>
 </sst>
 </file>
@@ -738,7 +741,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -766,6 +769,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -852,7 +873,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -937,6 +958,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,9 +969,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF66FF66"/>
       <color rgb="FF000000"/>
       <color rgb="FFFF6600"/>
-      <color rgb="FF66FF66"/>
       <color rgb="FFFFCC00"/>
       <color rgb="FF08E622"/>
       <color rgb="FFFFFFFF"/>
@@ -984,7 +1008,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1033,7 +1057,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1082,7 +1106,7 @@
         <xdr:cNvPr id="3" name="Rectángulo: esquinas redondeadas 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,7 +1164,7 @@
         <xdr:cNvPr id="4" name="Rectángulo 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1211,7 +1235,7 @@
         <xdr:cNvPr id="5" name="Elipse 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1277,7 +1301,7 @@
         <xdr:cNvPr id="6" name="Flecha: a la derecha 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1337,7 +1361,7 @@
         <xdr:cNvPr id="7" name="Flecha: a la derecha 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1397,7 +1421,7 @@
         <xdr:cNvPr id="8" name="Flecha: a la derecha 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1457,7 +1481,7 @@
         <xdr:cNvPr id="9" name="Rectángulo 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1528,7 +1552,7 @@
         <xdr:cNvPr id="10" name="Rombo 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1599,7 +1623,7 @@
         <xdr:cNvPr id="11" name="Flecha: a la derecha 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1659,7 +1683,7 @@
         <xdr:cNvPr id="12" name="Flecha: a la derecha 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1719,7 +1743,7 @@
         <xdr:cNvPr id="13" name="Rectángulo 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1785,7 +1809,7 @@
         <xdr:cNvPr id="14" name="Flecha: a la derecha 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1845,7 +1869,7 @@
         <xdr:cNvPr id="15" name="Rectángulo 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1911,7 +1935,7 @@
         <xdr:cNvPr id="16" name="Rectángulo 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000010000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1977,7 +2001,7 @@
         <xdr:cNvPr id="17" name="Rectángulo 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000011000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000011000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2048,7 +2072,7 @@
         <xdr:cNvPr id="19" name="Rectángulo 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000013000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2114,7 +2138,7 @@
         <xdr:cNvPr id="20" name="Rectángulo 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000014000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000014000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2180,7 +2204,7 @@
         <xdr:cNvPr id="21" name="Rectángulo 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000015000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2251,7 +2275,7 @@
         <xdr:cNvPr id="22" name="Rombo 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000016000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2318,7 +2342,7 @@
         <xdr:cNvPr id="23" name="Flecha: a la derecha 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000017000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000017000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2378,7 +2402,7 @@
         <xdr:cNvPr id="24" name="Rectángulo 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000018000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2444,7 +2468,7 @@
         <xdr:cNvPr id="25" name="Rectángulo 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000019000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000019000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2510,7 +2534,7 @@
         <xdr:cNvPr id="27" name="Conector: angular 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2565,7 +2589,7 @@
         <xdr:cNvPr id="29" name="Conector: angular 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00001D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2620,7 +2644,7 @@
         <xdr:cNvPr id="40" name="Conector recto de flecha 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000028000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000028000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2676,7 +2700,7 @@
         <xdr:cNvPr id="41" name="Rectángulo 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000029000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000029000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2753,7 +2777,7 @@
         <xdr:cNvPr id="42" name="Flecha: a la derecha 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2813,7 +2837,7 @@
         <xdr:cNvPr id="43" name="Rectángulo 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2884,7 +2908,7 @@
         <xdr:cNvPr id="44" name="Flecha: a la derecha 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2944,7 +2968,7 @@
         <xdr:cNvPr id="45" name="Rectángulo 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3015,7 +3039,7 @@
         <xdr:cNvPr id="46" name="Flecha: a la derecha 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3075,7 +3099,7 @@
         <xdr:cNvPr id="47" name="Rectángulo 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3146,7 +3170,7 @@
         <xdr:cNvPr id="53" name="Conector: angular 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000035000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000035000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3201,7 +3225,7 @@
         <xdr:cNvPr id="59" name="Conector: angular 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00003B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3256,7 +3280,7 @@
         <xdr:cNvPr id="64" name="Rectángulo 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000040000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3327,7 +3351,7 @@
         <xdr:cNvPr id="66" name="Conector: angular 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000042000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3383,7 +3407,7 @@
         <xdr:cNvPr id="68" name="Conector: angular 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000044000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000044000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3439,7 +3463,7 @@
         <xdr:cNvPr id="70" name="Rectángulo 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000046000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000046000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3510,7 +3534,7 @@
         <xdr:cNvPr id="71" name="Flecha: a la derecha 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000047000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3570,7 +3594,7 @@
         <xdr:cNvPr id="72" name="Diagrama de flujo: datos 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000048000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3636,7 +3660,7 @@
         <xdr:cNvPr id="73" name="Flecha: a la derecha 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000049000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3696,7 +3720,7 @@
         <xdr:cNvPr id="74" name="Rectángulo 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3762,7 +3786,7 @@
         <xdr:cNvPr id="75" name="Rectángulo 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3833,7 +3857,7 @@
         <xdr:cNvPr id="76" name="Flecha: a la derecha 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3893,7 +3917,7 @@
         <xdr:cNvPr id="77" name="Rectángulo 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3959,7 +3983,7 @@
         <xdr:cNvPr id="78" name="Diagrama de flujo: datos 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4030,7 +4054,7 @@
         <xdr:cNvPr id="79" name="Flecha: a la derecha 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00004F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00004F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4090,7 +4114,7 @@
         <xdr:cNvPr id="80" name="Rectángulo 79">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000050000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000050000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4156,7 +4180,7 @@
         <xdr:cNvPr id="81" name="Flecha: a la derecha 80">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000051000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000051000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4216,7 +4240,7 @@
         <xdr:cNvPr id="52" name="Rectángulo 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000034000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000034000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4287,7 +4311,7 @@
         <xdr:cNvPr id="57" name="Rectángulo 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000039000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000039000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4364,7 +4388,7 @@
         <xdr:cNvPr id="60" name="Rectángulo 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-00003C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4715,7 +4739,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6870,9 +6894,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32"/>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="38" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="27"/>
@@ -6900,7 +6924,7 @@
       <c r="W14" s="17"/>
       <c r="X14" s="17"/>
     </row>
-    <row r="15" spans="1:25" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A15" s="32"/>
       <c r="B15" s="28" t="s">
         <v>145</v>
@@ -6928,7 +6952,7 @@
       <c r="W15" s="16"/>
       <c r="X15" s="16"/>
     </row>
-    <row r="16" spans="1:25" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="28" t="s">
         <v>146</v>
@@ -6956,7 +6980,7 @@
       <c r="W16" s="16"/>
       <c r="X16" s="16"/>
     </row>
-    <row r="17" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A17" s="32"/>
       <c r="B17" s="28" t="s">
         <v>147</v>
@@ -6984,7 +7008,7 @@
       <c r="W17" s="16"/>
       <c r="X17" s="16"/>
     </row>
-    <row r="18" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
       <c r="B18" s="28" t="s">
         <v>148</v>
@@ -7014,7 +7038,7 @@
     </row>
     <row r="19" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="36" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="28"/>
@@ -7840,7 +7864,7 @@
     </row>
     <row r="41" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32"/>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="36" t="s">
         <v>91</v>
       </c>
       <c r="C41" s="28"/>
@@ -7970,7 +7994,7 @@
     </row>
     <row r="45" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="28" t="s">
@@ -8096,9 +8120,9 @@
       <c r="W48" s="16"/>
       <c r="X48" s="16"/>
     </row>
-    <row r="49" spans="1:24" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32"/>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="36" t="s">
         <v>85</v>
       </c>
       <c r="C49" s="28"/>
@@ -8126,7 +8150,7 @@
       <c r="W49" s="16"/>
       <c r="X49" s="16"/>
     </row>
-    <row r="50" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A50" s="32"/>
       <c r="B50" s="28" t="s">
         <v>83</v>
@@ -8164,7 +8188,7 @@
       <c r="W50" s="16"/>
       <c r="X50" s="16"/>
     </row>
-    <row r="51" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A51" s="32"/>
       <c r="B51" s="28" t="s">
         <v>84</v>
@@ -8198,7 +8222,7 @@
       <c r="W51" s="16"/>
       <c r="X51" s="16"/>
     </row>
-    <row r="52" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A52" s="32"/>
       <c r="B52" s="28" t="s">
         <v>86</v>
@@ -8228,7 +8252,7 @@
       <c r="W52" s="16"/>
       <c r="X52" s="16"/>
     </row>
-    <row r="53" spans="1:24" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A53" s="32"/>
       <c r="B53" s="27" t="s">
         <v>197</v>
@@ -8260,7 +8284,7 @@
       <c r="W53" s="16"/>
       <c r="X53" s="16"/>
     </row>
-    <row r="54" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A54" s="32"/>
       <c r="B54" s="28" t="s">
         <v>165</v>
@@ -8290,7 +8314,7 @@
       <c r="W54" s="16"/>
       <c r="X54" s="16"/>
     </row>
-    <row r="55" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A55" s="32"/>
       <c r="B55" s="28" t="s">
         <v>166</v>
@@ -8338,9 +8362,9 @@
       <c r="W55" s="16"/>
       <c r="X55" s="16"/>
     </row>
-    <row r="56" spans="1:24" s="4" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="4" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A56" s="32"/>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="36" t="s">
         <v>100</v>
       </c>
       <c r="C56" s="28" t="s">
@@ -8370,7 +8394,7 @@
       <c r="W56" s="17"/>
       <c r="X56" s="17"/>
     </row>
-    <row r="57" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A57" s="32"/>
       <c r="B57" s="28" t="s">
         <v>162</v>
@@ -8400,7 +8424,7 @@
       <c r="W57" s="16"/>
       <c r="X57" s="16"/>
     </row>
-    <row r="58" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A58" s="32"/>
       <c r="B58" s="28" t="s">
         <v>163</v>
@@ -8430,9 +8454,9 @@
       <c r="W58" s="16"/>
       <c r="X58" s="16"/>
     </row>
-    <row r="59" spans="1:24" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32"/>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="36" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="28" t="s">
@@ -8462,7 +8486,7 @@
       <c r="W59" s="16"/>
       <c r="X59" s="16"/>
     </row>
-    <row r="60" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A60" s="32"/>
       <c r="B60" s="28" t="s">
         <v>88</v>
@@ -8514,7 +8538,7 @@
       </c>
       <c r="X60" s="16"/>
     </row>
-    <row r="61" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A61" s="32"/>
       <c r="B61" s="28" t="s">
         <v>89</v>
@@ -8552,7 +8576,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A62" s="32"/>
       <c r="B62" s="28" t="s">
         <v>90</v>
@@ -8584,7 +8608,7 @@
       <c r="W62" s="16"/>
       <c r="X62" s="16"/>
     </row>
-    <row r="63" spans="1:24" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A63" s="32"/>
       <c r="B63" s="27" t="s">
         <v>150</v>
@@ -8614,7 +8638,7 @@
       <c r="W63" s="16"/>
       <c r="X63" s="16"/>
     </row>
-    <row r="64" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A64" s="32"/>
       <c r="B64" s="28" t="s">
         <v>92</v>
@@ -8666,7 +8690,7 @@
       </c>
       <c r="X64" s="16"/>
     </row>
-    <row r="65" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A65" s="32"/>
       <c r="B65" s="28" t="s">
         <v>151</v>
@@ -8694,7 +8718,7 @@
       <c r="W65" s="16"/>
       <c r="X65" s="16"/>
     </row>
-    <row r="66" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A66" s="32"/>
       <c r="B66" s="28" t="s">
         <v>152</v>
@@ -9740,9 +9764,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="85" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A85" s="32"/>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="38" t="s">
         <v>167</v>
       </c>
       <c r="C85" s="28" t="s">
@@ -9772,7 +9796,7 @@
       <c r="W85" s="17"/>
       <c r="X85" s="17"/>
     </row>
-    <row r="86" spans="1:24" s="4" customFormat="1" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A86" s="32"/>
       <c r="B86" s="28" t="s">
         <v>168</v>
@@ -9800,7 +9824,7 @@
       <c r="W86" s="17"/>
       <c r="X86" s="17"/>
     </row>
-    <row r="87" spans="1:24" s="4" customFormat="1" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A87" s="32"/>
       <c r="B87" s="28" t="s">
         <v>169</v>
@@ -9828,9 +9852,9 @@
       <c r="W87" s="17"/>
       <c r="X87" s="17"/>
     </row>
-    <row r="88" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="32"/>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="38" t="s">
         <v>170</v>
       </c>
       <c r="C88" s="28" t="s">
@@ -9860,7 +9884,7 @@
       <c r="W88" s="17"/>
       <c r="X88" s="17"/>
     </row>
-    <row r="89" spans="1:24" s="4" customFormat="1" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A89" s="32"/>
       <c r="B89" s="28" t="s">
         <v>171</v>
@@ -9888,7 +9912,7 @@
       <c r="W89" s="17"/>
       <c r="X89" s="17"/>
     </row>
-    <row r="90" spans="1:24" s="4" customFormat="1" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" s="4" customFormat="1" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A90" s="32"/>
       <c r="B90" s="28" t="s">
         <v>199</v>
@@ -9916,7 +9940,7 @@
       <c r="W90" s="17"/>
       <c r="X90" s="17"/>
     </row>
-    <row r="91" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A91" s="32"/>
       <c r="B91" s="28" t="s">
         <v>172</v>
@@ -9944,7 +9968,7 @@
       <c r="W91" s="16"/>
       <c r="X91" s="16"/>
     </row>
-    <row r="92" spans="1:24" ht="14.45" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" ht="14.45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A92" s="32"/>
       <c r="B92" s="28" t="s">
         <v>173</v>
@@ -9983,7 +10007,9 @@
       <c r="D93" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E93" s="10"/>
+      <c r="E93" s="10" t="s">
+        <v>216</v>
+      </c>
       <c r="F93" s="17"/>
       <c r="G93" s="17"/>
       <c r="H93" s="17"/>
@@ -10072,7 +10098,7 @@
       <c r="W95" s="16"/>
       <c r="X95" s="16"/>
     </row>
-    <row r="96" spans="1:24" s="4" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:24" s="4" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A96" s="32"/>
       <c r="B96" s="27" t="s">
         <v>174</v>
@@ -10102,7 +10128,7 @@
       <c r="W96" s="17"/>
       <c r="X96" s="17"/>
     </row>
-    <row r="97" spans="1:24" s="4" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" s="4" customFormat="1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="10" t="s">
         <v>175</v>
@@ -10130,7 +10156,7 @@
       <c r="W97" s="17"/>
       <c r="X97" s="17"/>
     </row>
-    <row r="98" spans="1:24" s="4" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:24" s="4" customFormat="1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
       <c r="B98" s="10" t="s">
         <v>176</v>
@@ -10158,7 +10184,7 @@
       <c r="W98" s="17"/>
       <c r="X98" s="17"/>
     </row>
-    <row r="99" spans="1:24" s="4" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:24" s="4" customFormat="1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
       <c r="B99" s="10" t="s">
         <v>177</v>
@@ -10186,7 +10212,7 @@
       <c r="W99" s="17"/>
       <c r="X99" s="17"/>
     </row>
-    <row r="100" spans="1:24" s="4" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" s="4" customFormat="1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="20" t="s">
         <v>148</v>
